--- a/data/trans_orig/P33B4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023</t>
+          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38262</t>
+          <t>37421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>57912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33804</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49224</t>
+          <t>49513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59397</t>
+          <t>56979</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>47287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43102</t>
+          <t>44218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87747</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311793</t>
+          <t>312782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>360050</t>
+          <t>361022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221974</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263349</t>
+          <t>263687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>553119</t>
+          <t>549956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>613858</t>
+          <t>613312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29908</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61923</t>
+          <t>61657</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>39047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73582</t>
+          <t>74472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>60245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79713</t>
+          <t>79816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74076</t>
+          <t>77418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126884</t>
+          <t>127315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>326858</t>
+          <t>323210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>365052</t>
+          <t>363841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>357596</t>
+          <t>358307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>429808</t>
+          <t>434901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>698104</t>
+          <t>699241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>785208</t>
+          <t>782328</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>47284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>37113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58850</t>
+          <t>58978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66972</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>98891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50371</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>55268</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64364</t>
+          <t>64272</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>95415</t>
+          <t>96886</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62891</t>
+          <t>62529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96089</t>
+          <t>96351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99699</t>
+          <t>99323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131363</t>
+          <t>131832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172736</t>
+          <t>171273</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217446</t>
+          <t>220321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361811</t>
+          <t>363655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403608</t>
+          <t>404060</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318172</t>
+          <t>319758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>354865</t>
+          <t>357205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>693755</t>
+          <t>689950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>749409</t>
+          <t>749999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64310</t>
+          <t>64145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62207</t>
+          <t>62348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93432</t>
+          <t>91797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69313</t>
+          <t>71637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147979</t>
+          <t>150148</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70370</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65408</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99878</t>
+          <t>100174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79983</t>
+          <t>78801</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162878</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>51928</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194561</t>
+          <t>190237</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,82 +2678,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>156862</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>130578</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>176911</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>287814</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>183924</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>350767</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>17,99%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>21,92%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>156862</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>134185</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>176917</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>287814</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>159636</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>347352</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>573791</t>
+          <t>571608</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>784607</t>
+          <t>792768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>371799</t>
+          <t>372065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>446069</t>
+          <t>455016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>957402</t>
+          <t>952677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1298304</t>
+          <t>1258847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39675</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66459</t>
+          <t>63367</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66949</t>
+          <t>67362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91548</t>
+          <t>91830</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>113692</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148800</t>
+          <t>149554</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>30047</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52358</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72666</t>
+          <t>72544</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96408</t>
+          <t>96515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107781</t>
+          <t>107819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>142083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96897</t>
+          <t>97237</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131701</t>
+          <t>130563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115747</t>
+          <t>115853</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144256</t>
+          <t>143443</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>221064</t>
+          <t>219836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>265248</t>
+          <t>264109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>333397</t>
+          <t>333753</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>376006</t>
+          <t>376594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>237274</t>
+          <t>235609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>273290</t>
+          <t>269834</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>581535</t>
+          <t>583209</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>637048</t>
+          <t>637556</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43544</t>
+          <t>42544</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24422</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98886</t>
+          <t>100604</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>51658</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129341</t>
+          <t>129481</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>66733</t>
+          <t>67316</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36414</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>88011</t>
+          <t>88711</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69578</t>
+          <t>68782</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>95025</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>44934</t>
+          <t>51614</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>171173</t>
+          <t>172516</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>105649</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>251474</t>
+          <t>252170</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>211883</t>
+          <t>212195</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>241646</t>
+          <t>242163</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>279264</t>
+          <t>278368</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>520883</t>
+          <t>506007</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>518044</t>
+          <t>518698</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>784023</t>
+          <t>783071</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30222</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>47216</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>67838</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>90226</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>105080</t>
+          <t>103878</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>135295</t>
+          <t>133078</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46086</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>65571</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>78659</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>105305</t>
+          <t>103275</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>44173</t>
+          <t>45115</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64917</t>
+          <t>64751</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>101235</t>
+          <t>101463</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125492</t>
+          <t>126062</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>152342</t>
+          <t>151707</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>183971</t>
+          <t>184895</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>142189</t>
+          <t>143755</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>167861</t>
+          <t>168195</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>160917</t>
+          <t>161794</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>189460</t>
+          <t>191383</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>310337</t>
+          <t>313575</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>351802</t>
+          <t>350482</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>181082</t>
+          <t>177369</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269016</t>
+          <t>263324</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>322468</t>
+          <t>325484</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>439173</t>
+          <t>442484</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>542694</t>
+          <t>539818</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>685879</t>
+          <t>688374</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>166969</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>252133</t>
+          <t>245787</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>291459</t>
+          <t>294772</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>395914</t>
+          <t>398918</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>492553</t>
+          <t>489633</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>629771</t>
+          <t>628626</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>416153</t>
+          <t>420911</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>596419</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>558095</t>
+          <t>593034</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>776492</t>
+          <t>780988</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1101163</t>
+          <t>1082395</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1350563</t>
+          <t>1353174</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2376978</t>
+          <t>2386119</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2696543</t>
+          <t>2698960</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2069052</t>
+          <t>2063538</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2499607</t>
+          <t>2469347</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4493867</t>
+          <t>4487466</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4959207</t>
+          <t>5001639</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37421</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>44587</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57912</t>
+          <t>66538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28827</t>
+          <t>35741</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>55480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>31578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18482</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56979</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>21691</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>52776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63403</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>46115</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>340670</t>
+          <t>345200</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>312782</t>
+          <t>320345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>361022</t>
+          <t>365780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>244650</t>
+          <t>279023</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223266</t>
+          <t>254000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263687</t>
+          <t>299609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>585320</t>
+          <t>624223</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549956</t>
+          <t>590522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>613312</t>
+          <t>654643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>33051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>44446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>43607</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>32190</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61657</t>
+          <t>64300</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34822</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>52642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54374</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39047</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74472</t>
+          <t>77969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>56887</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60245</t>
+          <t>78371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61303</t>
+          <t>73434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38584</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79816</t>
+          <t>91899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>103611</t>
+          <t>130321</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>107176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>153301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>346487</t>
+          <t>379878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>323210</t>
+          <t>357199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>363841</t>
+          <t>400124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>386972</t>
+          <t>360383</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>358307</t>
+          <t>337326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>434901</t>
+          <t>381141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>733459</t>
+          <t>740261</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>699241</t>
+          <t>709930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>782328</t>
+          <t>770493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34832</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47284</t>
+          <t>51880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47375</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37113</t>
+          <t>44430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58978</t>
+          <t>68734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>93692</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67336</t>
+          <t>76286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>113312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>39575</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50073</t>
+          <t>54777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43016</t>
+          <t>52223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>41545</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>65319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>79329</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64272</t>
+          <t>76217</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96886</t>
+          <t>112796</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79128</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>71916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96351</t>
+          <t>106349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>114696</t>
+          <t>129022</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99323</t>
+          <t>113428</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>146363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>193824</t>
+          <t>217534</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171273</t>
+          <t>193107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>220321</t>
+          <t>241775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>384081</t>
+          <t>452417</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363655</t>
+          <t>427857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404060</t>
+          <t>475701</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>337380</t>
+          <t>385568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>319758</t>
+          <t>364489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357205</t>
+          <t>405967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>721461</t>
+          <t>837985</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>689950</t>
+          <t>804915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>749999</t>
+          <t>867488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>534353</t>
+          <t>618871</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>534353</t>
+          <t>618871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>534353</t>
+          <t>618871</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1076821</t>
+          <t>1241010</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1076821</t>
+          <t>1241010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1076821</t>
+          <t>1241010</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41665</t>
+          <t>45774</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64145</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77538</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62348</t>
+          <t>71945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91797</t>
+          <t>100528</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>119203</t>
+          <t>131839</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71637</t>
+          <t>112881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150148</t>
+          <t>152225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>49770</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>64774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81299</t>
+          <t>82561</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65356</t>
+          <t>68854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100174</t>
+          <t>96551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>127122</t>
+          <t>132331</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78801</t>
+          <t>114650</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163028</t>
+          <t>154361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130951</t>
+          <t>135628</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51928</t>
+          <t>115710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>190237</t>
+          <t>156039</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>156862</t>
+          <t>170514</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130578</t>
+          <t>152963</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>176911</t>
+          <t>189002</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>287814</t>
+          <t>306142</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>183924</t>
+          <t>278937</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>350767</t>
+          <t>335058</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>669347</t>
+          <t>469445</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>571608</t>
+          <t>445864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>792768</t>
+          <t>493790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>396799</t>
+          <t>397355</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>372065</t>
+          <t>376787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>455016</t>
+          <t>419097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1066146</t>
+          <t>866800</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>952677</t>
+          <t>833329</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1258847</t>
+          <t>901085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51768</t>
+          <t>55306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40271</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>69636</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78779</t>
+          <t>88073</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>75814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91830</t>
+          <t>103574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>130547</t>
+          <t>143379</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>113692</t>
+          <t>125456</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149554</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>39852</t>
+          <t>41639</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30047</t>
+          <t>30724</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>54422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>83809</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72544</t>
+          <t>81574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96515</t>
+          <t>108264</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>123661</t>
+          <t>136377</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107819</t>
+          <t>117818</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142083</t>
+          <t>155728</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>113581</t>
+          <t>124683</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97237</t>
+          <t>107064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>144863</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>129716</t>
+          <t>143358</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115853</t>
+          <t>128728</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143443</t>
+          <t>160493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>243296</t>
+          <t>268041</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>219836</t>
+          <t>246190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264109</t>
+          <t>293711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>355003</t>
+          <t>386637</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>333753</t>
+          <t>362984</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>376594</t>
+          <t>407735</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>253263</t>
+          <t>281964</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>235609</t>
+          <t>261731</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>269834</t>
+          <t>300176</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>608266</t>
+          <t>668601</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>583209</t>
+          <t>641392</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>637556</t>
+          <t>696564</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42544</t>
+          <t>49183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>62919</t>
+          <t>70138</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>58987</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>80563</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>96805</t>
+          <t>108648</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>94292</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>123145</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>41267</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>35630</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67316</t>
+          <t>54575</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>66059</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>88711</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>90789</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95025</t>
+          <t>106393</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>109596</t>
+          <t>119282</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>51614</t>
+          <t>106132</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>172516</t>
+          <t>133107</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>191667</t>
+          <t>210071</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105649</t>
+          <t>190832</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>252170</t>
+          <t>230271</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>227415</t>
+          <t>251410</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>212195</t>
+          <t>233575</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>242163</t>
+          <t>267520</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>394587</t>
+          <t>205152</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>278368</t>
+          <t>189239</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>506007</t>
+          <t>220706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>622001</t>
+          <t>456561</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>518698</t>
+          <t>434046</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>783071</t>
+          <t>478973</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>47216</t>
+          <t>55865</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>79538</t>
+          <t>89284</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>77684</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>101769</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>117817</t>
+          <t>132865</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>103878</t>
+          <t>118468</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>133078</t>
+          <t>151335</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>37818</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>47122</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>55677</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46634</t>
+          <t>51442</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>65571</t>
+          <t>72595</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>90568</t>
+          <t>98924</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>86020</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>103275</t>
+          <t>114413</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45115</t>
+          <t>49998</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64751</t>
+          <t>72953</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>113802</t>
+          <t>121299</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>101463</t>
+          <t>107574</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>135025</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>168071</t>
+          <t>182371</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>151707</t>
+          <t>163971</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>184895</t>
+          <t>200421</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>155320</t>
+          <t>167729</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>143755</t>
+          <t>152616</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>168195</t>
+          <t>181613</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>175761</t>
+          <t>191763</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>161794</t>
+          <t>176539</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>191383</t>
+          <t>207968</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>331081</t>
+          <t>359493</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>313575</t>
+          <t>338529</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>350482</t>
+          <t>382023</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>424778</t>
+          <t>463453</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>424778</t>
+          <t>463453</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>424778</t>
+          <t>463453</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>707537</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>707537</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>707537</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>255982</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>177369</t>
+          <t>225833</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>263324</t>
+          <t>293588</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>395677</t>
+          <t>446667</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>325484</t>
+          <t>413139</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>442484</t>
+          <t>482837</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>625822</t>
+          <t>702649</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>539818</t>
+          <t>658065</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>688374</t>
+          <t>746046</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>212662</t>
+          <t>231868</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>165236</t>
+          <t>202198</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>265009</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>357278</t>
+          <t>394021</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>294772</t>
+          <t>364310</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>398918</t>
+          <t>429016</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>569940</t>
+          <t>625889</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>489633</t>
+          <t>583161</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>670415</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>535671</t>
+          <t>589148</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>420911</t>
+          <t>544484</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>596419</t>
+          <t>634522</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>716015</t>
+          <t>791085</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>593034</t>
+          <t>752845</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>780988</t>
+          <t>834586</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1251686</t>
+          <t>1380233</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1082395</t>
+          <t>1322087</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1353174</t>
+          <t>1450693</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2478324</t>
+          <t>2452716</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2386119</t>
+          <t>2389852</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2698960</t>
+          <t>2511758</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2189412</t>
+          <t>2101209</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2063538</t>
+          <t>2049436</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2469347</t>
+          <t>2150649</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4667736</t>
+          <t>4553925</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4487466</t>
+          <t>4468313</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5001639</t>
+          <t>4630232</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
